--- a/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
+++ b/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>438</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.0593607305936073</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>389</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.1670951156812339</v>
+        <v>65</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>516</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.1182170542635659</v>
+        <v>61</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>458</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.2620087336244541</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>562</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.300711743772242</v>
+        <v>169</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>257</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.4007782101167315</v>
+        <v>103</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>534</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.07677902621722846</v>
+        <v>41</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>219</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.0228310502283105</v>
+        <v>5</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>347</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.005763688760806916</v>
+        <v>2</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>494</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.1417004048582996</v>
+        <v>70</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>620</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.07903225806451612</v>
+        <v>49</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>256</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.1796875</v>
+        <v>46</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>314</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.1082802547770701</v>
+        <v>34</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>401</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.04738154613466334</v>
+        <v>19</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>326</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.3128834355828221</v>
+        <v>102</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>234</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.03846153846153846</v>
+        <v>9</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>337</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.01483679525222552</v>
+        <v>5</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>153</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.1830065359477124</v>
+        <v>28</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>320</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.778125</v>
+        <v>249</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>294</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0.1530612244897959</v>
+        <v>45</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>144</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0.6597222222222222</v>
+        <v>95</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>103</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>0.009708737864077669</v>
+        <v>1</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>162</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>0.02469135802469136</v>
+        <v>4</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>227</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0.03083700440528634</v>
+        <v>7</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>293</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>0.05460750853242321</v>
+        <v>16</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>147</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>0.01360544217687075</v>
+        <v>2</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>274</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>0.0218978102189781</v>
+        <v>6</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>182</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>0.005494505494505495</v>
+        <v>1</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>228</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>0.03947368421052631</v>
+        <v>9</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>215</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>0.004651162790697674</v>
+        <v>1</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>170</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>0.2529411764705882</v>
+        <v>43</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>303</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>0.1188118811881188</v>
+        <v>36</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>150</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>0.5933333333333334</v>
+        <v>89</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>178</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>0.651685393258427</v>
+        <v>116</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>144</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>0.7708333333333334</v>
+        <v>111</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>241</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>0.004149377593360996</v>
+        <v>1</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>120</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>0.4916666666666666</v>
+        <v>59</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>186</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>0.09677419354838709</v>
+        <v>18</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>184</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>0.4239130434782609</v>
+        <v>78</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>93</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>0.3333333333333333</v>
+        <v>31</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>225</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>0.09777777777777778</v>
+        <v>22</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>134</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>0.007462686567164179</v>
+        <v>1</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>322</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>0.03105590062111801</v>
+        <v>10</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>137</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>0.489051094890511</v>
+        <v>67</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>388</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>0.8891752577319587</v>
+        <v>345</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>299</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>0.04013377926421405</v>
+        <v>12</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>216</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>0.01388888888888889</v>
+        <v>3</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>59</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>0.1864406779661017</v>
+        <v>11</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>151</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>0.3642384105960265</v>
+        <v>55</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>151</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>0.2052980132450331</v>
+        <v>31</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>169</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>0.0650887573964497</v>
+        <v>11</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>158</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>0.7278481012658228</v>
+        <v>115</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>137</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>0.0291970802919708</v>
+        <v>4</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>134</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>0.03731343283582089</v>
+        <v>5</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>206</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>0.6456310679611651</v>
+        <v>133</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>274</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>0.0072992700729927</v>
+        <v>2</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>211</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>0.08056872037914692</v>
+        <v>17</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>119</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>0.5966386554621849</v>
+        <v>71</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>200</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>0.235</v>
+        <v>47</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>233</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>0.02575107296137339</v>
+        <v>6</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>173</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>0.03468208092485549</v>
+        <v>6</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>322</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>0.04968944099378882</v>
+        <v>16</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>176</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>0.1420454545454546</v>
+        <v>25</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>89</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>0.1348314606741573</v>
+        <v>12</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>153</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>0.08496732026143791</v>
+        <v>13</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>73</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>0.6575342465753424</v>
+        <v>48</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>184</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0.3043478260869565</v>
+        <v>56</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>109</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>0.009174311926605505</v>
+        <v>1</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>100</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.13</v>
+        <v>13</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>157</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.03821656050955414</v>
+        <v>6</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>173</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0.3005780346820809</v>
+        <v>52</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>284</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.0352112676056338</v>
+        <v>10</v>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>236</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.0423728813559322</v>
+        <v>10</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>203</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.7684729064039408</v>
+        <v>156</v>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>184</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0.05434782608695652</v>
+        <v>10</v>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>164</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.1951219512195122</v>
+        <v>32</v>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         <v>256</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.046875</v>
+        <v>12</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>241</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0.04149377593360996</v>
+        <v>10</v>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>265</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.007547169811320755</v>
+        <v>2</v>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>151</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0.03311258278145696</v>
+        <v>5</v>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>302</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.04304635761589404</v>
+        <v>13</v>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>166</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.108433734939759</v>
+        <v>18</v>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>215</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>0.05116279069767442</v>
+        <v>11</v>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>173</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.09826589595375723</v>
+        <v>17</v>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>145</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>0.2689655172413793</v>
+        <v>39</v>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>276</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.007246376811594203</v>
+        <v>2</v>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>130</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>0.1615384615384615</v>
+        <v>21</v>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>162</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>0.1851851851851852</v>
+        <v>30</v>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>176</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>0.2102272727272727</v>
+        <v>37</v>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>328</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>0.02134146341463415</v>
+        <v>7</v>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>185</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>0.01081081081081081</v>
+        <v>2</v>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>161</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>0.6459627329192547</v>
+        <v>104</v>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>187</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>0.2513368983957219</v>
+        <v>47</v>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>164</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>0.8780487804878049</v>
+        <v>144</v>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>152</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>0.0131578947368421</v>
+        <v>2</v>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>161</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>0.04347826086956522</v>
+        <v>7</v>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>117</v>
       </c>
       <c r="M112" s="12" t="n">
-        <v>0.5897435897435898</v>
+        <v>69</v>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>113</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>0.1946902654867257</v>
+        <v>22</v>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>105</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>0.3904761904761905</v>
+        <v>41</v>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>198</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>0.005050505050505051</v>
+        <v>1</v>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>104</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>0.09615384615384616</v>
+        <v>10</v>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>185</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>0.2216216216216216</v>
+        <v>41</v>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>113</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>0.01769911504424779</v>
+        <v>2</v>
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>353</v>
       </c>
       <c r="M121" s="12" t="n">
-        <v>0.0084985835694051</v>
+        <v>3</v>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>169</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>0.005917159763313609</v>
+        <v>1</v>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>154</v>
       </c>
       <c r="M123" s="12" t="n">
-        <v>0.02597402597402598</v>
+        <v>4</v>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>173</v>
       </c>
       <c r="M124" s="12" t="n">
-        <v>0.138728323699422</v>
+        <v>24</v>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>167</v>
       </c>
       <c r="M125" s="12" t="n">
-        <v>0.3652694610778443</v>
+        <v>61</v>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>185</v>
       </c>
       <c r="M126" s="12" t="n">
-        <v>0.02702702702702703</v>
+        <v>5</v>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>67</v>
       </c>
       <c r="M128" s="12" t="n">
-        <v>0.1791044776119403</v>
+        <v>12</v>
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>189</v>
       </c>
       <c r="M129" s="12" t="n">
-        <v>0.04761904761904762</v>
+        <v>9</v>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         <v>208</v>
       </c>
       <c r="M130" s="12" t="n">
-        <v>0.09615384615384616</v>
+        <v>20</v>
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>221</v>
       </c>
       <c r="M131" s="12" t="n">
-        <v>0.02714932126696833</v>
+        <v>6</v>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>179</v>
       </c>
       <c r="M132" s="12" t="n">
-        <v>0.08379888268156424</v>
+        <v>15</v>
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>139</v>
       </c>
       <c r="M133" s="12" t="n">
-        <v>0.04316546762589928</v>
+        <v>6</v>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>122</v>
       </c>
       <c r="M134" s="12" t="n">
-        <v>0.03278688524590164</v>
+        <v>4</v>
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>119</v>
       </c>
       <c r="M135" s="12" t="n">
-        <v>0.2689075630252101</v>
+        <v>32</v>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>61</v>
       </c>
       <c r="M136" s="12" t="n">
-        <v>0.7540983606557377</v>
+        <v>46</v>
       </c>
       <c r="N136" s="2" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>118</v>
       </c>
       <c r="M137" s="12" t="n">
-        <v>0.02542372881355932</v>
+        <v>3</v>
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>128</v>
       </c>
       <c r="M138" s="12" t="n">
-        <v>0.0625</v>
+        <v>8</v>
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>192</v>
       </c>
       <c r="M139" s="12" t="n">
-        <v>0.03125</v>
+        <v>6</v>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>276</v>
       </c>
       <c r="M140" s="12" t="n">
-        <v>0.0108695652173913</v>
+        <v>3</v>
       </c>
       <c r="N140" s="2" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>101</v>
       </c>
       <c r="M141" s="12" t="n">
-        <v>0.7821782178217822</v>
+        <v>79</v>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>237</v>
       </c>
       <c r="M143" s="12" t="n">
-        <v>0.008438818565400843</v>
+        <v>2</v>
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>117</v>
       </c>
       <c r="M144" s="12" t="n">
-        <v>0.3675213675213675</v>
+        <v>43</v>
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>80</v>
       </c>
       <c r="M145" s="12" t="n">
-        <v>0.025</v>
+        <v>2</v>
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>90</v>
       </c>
       <c r="M146" s="12" t="n">
-        <v>0.1222222222222222</v>
+        <v>11</v>
       </c>
       <c r="N146" s="2" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>279</v>
       </c>
       <c r="M147" s="12" t="n">
-        <v>0.1612903225806452</v>
+        <v>45</v>
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>107</v>
       </c>
       <c r="M148" s="12" t="n">
-        <v>0.02803738317757009</v>
+        <v>3</v>
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>47</v>
       </c>
       <c r="M149" s="12" t="n">
-        <v>0.2127659574468085</v>
+        <v>10</v>
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>83</v>
       </c>
       <c r="M150" s="12" t="n">
-        <v>0.4096385542168675</v>
+        <v>34</v>
       </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>243</v>
       </c>
       <c r="M152" s="12" t="n">
-        <v>0.2716049382716049</v>
+        <v>66</v>
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>214</v>
       </c>
       <c r="M153" s="12" t="n">
-        <v>0.3551401869158878</v>
+        <v>76</v>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>142</v>
       </c>
       <c r="M154" s="12" t="n">
-        <v>0.2253521126760563</v>
+        <v>32</v>
       </c>
       <c r="N154" s="2" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>160</v>
       </c>
       <c r="M157" s="12" t="n">
-        <v>0.2125</v>
+        <v>34</v>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>212</v>
       </c>
       <c r="M159" s="12" t="n">
-        <v>0.169811320754717</v>
+        <v>36</v>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>114</v>
       </c>
       <c r="M160" s="12" t="n">
-        <v>0.04385964912280702</v>
+        <v>5</v>
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>173</v>
       </c>
       <c r="M161" s="12" t="n">
-        <v>0.02890173410404624</v>
+        <v>5</v>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>93</v>
       </c>
       <c r="M162" s="12" t="n">
-        <v>0.6021505376344086</v>
+        <v>56</v>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>90</v>
       </c>
       <c r="M163" s="12" t="n">
-        <v>0.2222222222222222</v>
+        <v>20</v>
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>129</v>
       </c>
       <c r="M164" s="12" t="n">
-        <v>0.09302325581395349</v>
+        <v>12</v>
       </c>
       <c r="N164" s="2" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>90</v>
       </c>
       <c r="M165" s="12" t="n">
-        <v>0.07777777777777778</v>
+        <v>7</v>
       </c>
       <c r="N165" s="2" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>123</v>
       </c>
       <c r="M166" s="12" t="n">
-        <v>0.02439024390243903</v>
+        <v>3</v>
       </c>
       <c r="N166" s="2" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>50</v>
       </c>
       <c r="M167" s="12" t="n">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>96</v>
       </c>
       <c r="M168" s="12" t="n">
-        <v>0.01041666666666667</v>
+        <v>1</v>
       </c>
       <c r="N168" s="2" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>71</v>
       </c>
       <c r="M169" s="12" t="n">
-        <v>0.2816901408450704</v>
+        <v>20</v>
       </c>
       <c r="N169" s="2" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>176</v>
       </c>
       <c r="M170" s="12" t="n">
-        <v>0.3181818181818182</v>
+        <v>56</v>
       </c>
       <c r="N170" s="2" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>96</v>
       </c>
       <c r="M171" s="12" t="n">
-        <v>0.07291666666666667</v>
+        <v>7</v>
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>137</v>
       </c>
       <c r="M173" s="12" t="n">
-        <v>0.0218978102189781</v>
+        <v>3</v>
       </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>156</v>
       </c>
       <c r="M174" s="12" t="n">
-        <v>0.1474358974358974</v>
+        <v>23</v>
       </c>
       <c r="N174" s="2" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>29</v>
       </c>
       <c r="M175" s="12" t="n">
-        <v>0.2413793103448276</v>
+        <v>7</v>
       </c>
       <c r="N175" s="2" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>91</v>
       </c>
       <c r="M178" s="12" t="n">
-        <v>0.07692307692307693</v>
+        <v>7</v>
       </c>
       <c r="N178" s="2" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>117</v>
       </c>
       <c r="M180" s="12" t="n">
-        <v>0.3076923076923077</v>
+        <v>36</v>
       </c>
       <c r="N180" s="2" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>77</v>
       </c>
       <c r="M181" s="12" t="n">
-        <v>0.2987012987012987</v>
+        <v>23</v>
       </c>
       <c r="N181" s="2" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>169</v>
       </c>
       <c r="M182" s="12" t="n">
-        <v>0.0650887573964497</v>
+        <v>11</v>
       </c>
       <c r="N182" s="2" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>129</v>
       </c>
       <c r="M183" s="12" t="n">
-        <v>0.2248062015503876</v>
+        <v>29</v>
       </c>
       <c r="N183" s="2" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>108</v>
       </c>
       <c r="M184" s="12" t="n">
-        <v>0.3888888888888889</v>
+        <v>42</v>
       </c>
       <c r="N184" s="2" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>124</v>
       </c>
       <c r="M186" s="12" t="n">
-        <v>0.8629032258064516</v>
+        <v>107</v>
       </c>
       <c r="N186" s="2" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>117</v>
       </c>
       <c r="M188" s="12" t="n">
-        <v>0.1282051282051282</v>
+        <v>15</v>
       </c>
       <c r="N188" s="2" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>74</v>
       </c>
       <c r="M189" s="12" t="n">
-        <v>0.1891891891891892</v>
+        <v>14</v>
       </c>
       <c r="N189" s="2" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>83</v>
       </c>
       <c r="M190" s="12" t="n">
-        <v>0.04819277108433735</v>
+        <v>4</v>
       </c>
       <c r="N190" s="2" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>64</v>
       </c>
       <c r="M192" s="12" t="n">
-        <v>0.015625</v>
+        <v>1</v>
       </c>
       <c r="N192" s="2" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>111</v>
       </c>
       <c r="M193" s="12" t="n">
-        <v>0.02702702702702703</v>
+        <v>3</v>
       </c>
       <c r="N193" s="2" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>188</v>
       </c>
       <c r="M194" s="12" t="n">
-        <v>0.02659574468085106</v>
+        <v>5</v>
       </c>
       <c r="N194" s="2" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>206</v>
       </c>
       <c r="M195" s="12" t="n">
-        <v>0.1067961165048544</v>
+        <v>22</v>
       </c>
       <c r="N195" s="2" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>70</v>
       </c>
       <c r="M196" s="12" t="n">
-        <v>0.1285714285714286</v>
+        <v>9</v>
       </c>
       <c r="N196" s="2" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>95</v>
       </c>
       <c r="M197" s="12" t="n">
-        <v>0.2842105263157895</v>
+        <v>27</v>
       </c>
       <c r="N197" s="2" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>104</v>
       </c>
       <c r="M200" s="12" t="n">
-        <v>0.009615384615384616</v>
+        <v>1</v>
       </c>
       <c r="N200" s="2" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>148</v>
       </c>
       <c r="M201" s="12" t="n">
-        <v>0.006756756756756757</v>
+        <v>1</v>
       </c>
       <c r="N201" s="2" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>99</v>
       </c>
       <c r="M203" s="12" t="n">
-        <v>0.0101010101010101</v>
+        <v>1</v>
       </c>
       <c r="N203" s="2" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>138</v>
       </c>
       <c r="M204" s="12" t="n">
-        <v>0.01449275362318841</v>
+        <v>2</v>
       </c>
       <c r="N204" s="2" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>198</v>
       </c>
       <c r="M205" s="12" t="n">
-        <v>0.04040404040404041</v>
+        <v>8</v>
       </c>
       <c r="N205" s="2" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>71</v>
       </c>
       <c r="M206" s="12" t="n">
-        <v>0.2816901408450704</v>
+        <v>20</v>
       </c>
       <c r="N206" s="2" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>71</v>
       </c>
       <c r="M207" s="12" t="n">
-        <v>0.04225352112676056</v>
+        <v>3</v>
       </c>
       <c r="N207" s="2" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>157</v>
       </c>
       <c r="M208" s="12" t="n">
-        <v>0.286624203821656</v>
+        <v>45</v>
       </c>
       <c r="N208" s="2" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>63</v>
       </c>
       <c r="M209" s="12" t="n">
-        <v>0.4126984126984127</v>
+        <v>26</v>
       </c>
       <c r="N209" s="2" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>193</v>
       </c>
       <c r="M210" s="12" t="n">
-        <v>0.02072538860103627</v>
+        <v>4</v>
       </c>
       <c r="N210" s="2" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>64</v>
       </c>
       <c r="M211" s="12" t="n">
-        <v>0.1875</v>
+        <v>12</v>
       </c>
       <c r="N211" s="2" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>62</v>
       </c>
       <c r="M212" s="12" t="n">
-        <v>0.01612903225806452</v>
+        <v>1</v>
       </c>
       <c r="N212" s="2" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>77</v>
       </c>
       <c r="M214" s="12" t="n">
-        <v>0.02597402597402598</v>
+        <v>2</v>
       </c>
       <c r="N214" s="2" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>64</v>
       </c>
       <c r="M215" s="12" t="n">
-        <v>0.109375</v>
+        <v>7</v>
       </c>
       <c r="N215" s="2" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
         <v>90</v>
       </c>
       <c r="M216" s="12" t="n">
-        <v>0.2555555555555555</v>
+        <v>23</v>
       </c>
       <c r="N216" s="2" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>37</v>
       </c>
       <c r="M217" s="12" t="n">
-        <v>0.02702702702702703</v>
+        <v>1</v>
       </c>
       <c r="N217" s="2" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>69</v>
       </c>
       <c r="M218" s="12" t="n">
-        <v>0.08695652173913043</v>
+        <v>6</v>
       </c>
       <c r="N218" s="2" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         <v>126</v>
       </c>
       <c r="M219" s="12" t="n">
-        <v>0.4444444444444444</v>
+        <v>56</v>
       </c>
       <c r="N219" s="2" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>117</v>
       </c>
       <c r="M221" s="12" t="n">
-        <v>0.3675213675213675</v>
+        <v>43</v>
       </c>
       <c r="N221" s="2" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>78</v>
       </c>
       <c r="M223" s="12" t="n">
-        <v>0.05128205128205128</v>
+        <v>4</v>
       </c>
       <c r="N223" s="2" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>159</v>
       </c>
       <c r="M224" s="12" t="n">
-        <v>0.1006289308176101</v>
+        <v>16</v>
       </c>
       <c r="N224" s="2" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>101</v>
       </c>
       <c r="M226" s="12" t="n">
-        <v>0.2277227722772277</v>
+        <v>23</v>
       </c>
       <c r="N226" s="2" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>114</v>
       </c>
       <c r="M227" s="12" t="n">
-        <v>0.008771929824561403</v>
+        <v>1</v>
       </c>
       <c r="N227" s="2" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>145</v>
       </c>
       <c r="M228" s="12" t="n">
-        <v>0.1310344827586207</v>
+        <v>19</v>
       </c>
       <c r="N228" s="2" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>82</v>
       </c>
       <c r="M229" s="12" t="n">
-        <v>0.01219512195121951</v>
+        <v>1</v>
       </c>
       <c r="N229" s="2" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>71</v>
       </c>
       <c r="M230" s="12" t="n">
-        <v>0.01408450704225352</v>
+        <v>1</v>
       </c>
       <c r="N230" s="2" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>92</v>
       </c>
       <c r="M231" s="12" t="n">
-        <v>0.108695652173913</v>
+        <v>10</v>
       </c>
       <c r="N231" s="2" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>81</v>
       </c>
       <c r="M232" s="12" t="n">
-        <v>0.06172839506172839</v>
+        <v>5</v>
       </c>
       <c r="N232" s="2" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>106</v>
       </c>
       <c r="M233" s="12" t="n">
-        <v>0.01886792452830189</v>
+        <v>2</v>
       </c>
       <c r="N233" s="2" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>63</v>
       </c>
       <c r="M234" s="12" t="n">
-        <v>0.03174603174603174</v>
+        <v>2</v>
       </c>
       <c r="N234" s="2" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>86</v>
       </c>
       <c r="M235" s="12" t="n">
-        <v>0.2674418604651163</v>
+        <v>23</v>
       </c>
       <c r="N235" s="2" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>76</v>
       </c>
       <c r="M236" s="12" t="n">
-        <v>0.0131578947368421</v>
+        <v>1</v>
       </c>
       <c r="N236" s="2" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>100</v>
       </c>
       <c r="M237" s="12" t="n">
-        <v>0.27</v>
+        <v>27</v>
       </c>
       <c r="N237" s="2" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>66</v>
       </c>
       <c r="M240" s="12" t="n">
-        <v>0.4696969696969697</v>
+        <v>31</v>
       </c>
       <c r="N240" s="2" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>155</v>
       </c>
       <c r="M241" s="12" t="n">
-        <v>0.08387096774193549</v>
+        <v>13</v>
       </c>
       <c r="N241" s="2" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>102</v>
       </c>
       <c r="M242" s="12" t="n">
-        <v>0.08823529411764706</v>
+        <v>9</v>
       </c>
       <c r="N242" s="2" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>119</v>
       </c>
       <c r="M243" s="12" t="n">
-        <v>0.04201680672268908</v>
+        <v>5</v>
       </c>
       <c r="N243" s="2" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>66</v>
       </c>
       <c r="M244" s="12" t="n">
-        <v>0.7424242424242424</v>
+        <v>49</v>
       </c>
       <c r="N244" s="2" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>66</v>
       </c>
       <c r="M245" s="12" t="n">
-        <v>0.5303030303030303</v>
+        <v>35</v>
       </c>
       <c r="N245" s="2" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>117</v>
       </c>
       <c r="M246" s="12" t="n">
-        <v>0.03418803418803419</v>
+        <v>4</v>
       </c>
       <c r="N246" s="2" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>68</v>
       </c>
       <c r="M248" s="12" t="n">
-        <v>0.5882352941176471</v>
+        <v>40</v>
       </c>
       <c r="N248" s="2" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>146</v>
       </c>
       <c r="M249" s="12" t="n">
-        <v>0.03424657534246575</v>
+        <v>5</v>
       </c>
       <c r="N249" s="2" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>96</v>
       </c>
       <c r="M250" s="12" t="n">
-        <v>0.21875</v>
+        <v>21</v>
       </c>
       <c r="N250" s="2" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>77</v>
       </c>
       <c r="M251" s="12" t="n">
-        <v>0.3766233766233766</v>
+        <v>29</v>
       </c>
       <c r="N251" s="2" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>57</v>
       </c>
       <c r="M252" s="12" t="n">
-        <v>0.3859649122807017</v>
+        <v>22</v>
       </c>
       <c r="N252" s="2" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>65</v>
       </c>
       <c r="M254" s="12" t="n">
-        <v>0.03076923076923077</v>
+        <v>2</v>
       </c>
       <c r="N254" s="2" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>40</v>
       </c>
       <c r="M257" s="12" t="n">
-        <v>0.8</v>
+        <v>32</v>
       </c>
       <c r="N257" s="2" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>83</v>
       </c>
       <c r="M258" s="12" t="n">
-        <v>0.6746987951807228</v>
+        <v>56</v>
       </c>
       <c r="N258" s="2" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>123</v>
       </c>
       <c r="M260" s="12" t="n">
-        <v>0.1219512195121951</v>
+        <v>15</v>
       </c>
       <c r="N260" s="2" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>40</v>
       </c>
       <c r="M261" s="12" t="n">
-        <v>0.65</v>
+        <v>26</v>
       </c>
       <c r="N261" s="2" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>44</v>
       </c>
       <c r="M263" s="12" t="n">
-        <v>0.2045454545454546</v>
+        <v>9</v>
       </c>
       <c r="N263" s="2" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>67</v>
       </c>
       <c r="M264" s="12" t="n">
-        <v>0.07462686567164178</v>
+        <v>5</v>
       </c>
       <c r="N264" s="2" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>17</v>
       </c>
       <c r="M267" s="12" t="n">
-        <v>0.1764705882352941</v>
+        <v>3</v>
       </c>
       <c r="N267" s="2" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>139</v>
       </c>
       <c r="M269" s="12" t="n">
-        <v>0.04316546762589928</v>
+        <v>6</v>
       </c>
       <c r="N269" s="2" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>91</v>
       </c>
       <c r="M271" s="12" t="n">
-        <v>0.03296703296703297</v>
+        <v>3</v>
       </c>
       <c r="N271" s="2" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>84</v>
       </c>
       <c r="M272" s="12" t="n">
-        <v>0.04761904761904762</v>
+        <v>4</v>
       </c>
       <c r="N272" s="2" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>107</v>
       </c>
       <c r="M273" s="12" t="n">
-        <v>0.02803738317757009</v>
+        <v>3</v>
       </c>
       <c r="N273" s="2" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>40</v>
       </c>
       <c r="M275" s="12" t="n">
-        <v>0.775</v>
+        <v>31</v>
       </c>
       <c r="N275" s="2" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>56</v>
       </c>
       <c r="M276" s="12" t="n">
-        <v>0.75</v>
+        <v>42</v>
       </c>
       <c r="N276" s="2" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>69</v>
       </c>
       <c r="M277" s="12" t="n">
-        <v>0.1449275362318841</v>
+        <v>10</v>
       </c>
       <c r="N277" s="2" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>52</v>
       </c>
       <c r="M278" s="12" t="n">
-        <v>0.07692307692307693</v>
+        <v>4</v>
       </c>
       <c r="N278" s="2" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>42</v>
       </c>
       <c r="M279" s="12" t="n">
-        <v>0.07142857142857142</v>
+        <v>3</v>
       </c>
       <c r="N279" s="2" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>68</v>
       </c>
       <c r="M280" s="12" t="n">
-        <v>0.1911764705882353</v>
+        <v>13</v>
       </c>
       <c r="N280" s="2" t="inlineStr">
         <is>
@@ -15397,7 +15397,7 @@
         <v>78</v>
       </c>
       <c r="M281" s="12" t="n">
-        <v>0.2564102564102564</v>
+        <v>20</v>
       </c>
       <c r="N281" s="2" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>35</v>
       </c>
       <c r="M282" s="12" t="n">
-        <v>0.6285714285714286</v>
+        <v>22</v>
       </c>
       <c r="N282" s="2" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>96</v>
       </c>
       <c r="M284" s="12" t="n">
-        <v>0.34375</v>
+        <v>33</v>
       </c>
       <c r="N284" s="2" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>60</v>
       </c>
       <c r="M285" s="12" t="n">
-        <v>0.03333333333333333</v>
+        <v>2</v>
       </c>
       <c r="N285" s="2" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>53</v>
       </c>
       <c r="M286" s="12" t="n">
-        <v>0.6792452830188679</v>
+        <v>36</v>
       </c>
       <c r="N286" s="2" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>23</v>
       </c>
       <c r="M287" s="12" t="n">
-        <v>0.4347826086956522</v>
+        <v>10</v>
       </c>
       <c r="N287" s="2" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>63</v>
       </c>
       <c r="M288" s="12" t="n">
-        <v>0.01587301587301587</v>
+        <v>1</v>
       </c>
       <c r="N288" s="2" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>159</v>
       </c>
       <c r="M289" s="12" t="n">
-        <v>0.0440251572327044</v>
+        <v>7</v>
       </c>
       <c r="N289" s="2" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>47</v>
       </c>
       <c r="M290" s="12" t="n">
-        <v>0.0425531914893617</v>
+        <v>2</v>
       </c>
       <c r="N290" s="2" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>76</v>
       </c>
       <c r="M291" s="12" t="n">
-        <v>0.02631578947368421</v>
+        <v>2</v>
       </c>
       <c r="N291" s="2" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>36</v>
       </c>
       <c r="M294" s="12" t="n">
-        <v>0.25</v>
+        <v>9</v>
       </c>
       <c r="N294" s="2" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>54</v>
       </c>
       <c r="M295" s="12" t="n">
-        <v>0.1666666666666667</v>
+        <v>9</v>
       </c>
       <c r="N295" s="2" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>104</v>
       </c>
       <c r="M297" s="12" t="n">
-        <v>0.25</v>
+        <v>26</v>
       </c>
       <c r="N297" s="2" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>47</v>
       </c>
       <c r="M298" s="12" t="n">
-        <v>0.5957446808510638</v>
+        <v>28</v>
       </c>
       <c r="N298" s="2" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>59</v>
       </c>
       <c r="M299" s="12" t="n">
-        <v>0.05084745762711865</v>
+        <v>3</v>
       </c>
       <c r="N299" s="2" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>33</v>
       </c>
       <c r="M300" s="12" t="n">
-        <v>0.0303030303030303</v>
+        <v>1</v>
       </c>
       <c r="N300" s="2" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>32</v>
       </c>
       <c r="M301" s="12" t="n">
-        <v>0.40625</v>
+        <v>13</v>
       </c>
       <c r="N301" s="2" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>79</v>
       </c>
       <c r="M303" s="12" t="n">
-        <v>0.0379746835443038</v>
+        <v>3</v>
       </c>
       <c r="N303" s="2" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>81</v>
       </c>
       <c r="M304" s="12" t="n">
-        <v>0.03703703703703703</v>
+        <v>3</v>
       </c>
       <c r="N304" s="2" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>112</v>
       </c>
       <c r="M306" s="12" t="n">
-        <v>0.1696428571428572</v>
+        <v>19</v>
       </c>
       <c r="N306" s="2" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>110</v>
       </c>
       <c r="M307" s="12" t="n">
-        <v>0.5363636363636364</v>
+        <v>59</v>
       </c>
       <c r="N307" s="2" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>35</v>
       </c>
       <c r="M308" s="12" t="n">
-        <v>0.1142857142857143</v>
+        <v>4</v>
       </c>
       <c r="N308" s="2" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>72</v>
       </c>
       <c r="M309" s="12" t="n">
-        <v>0.25</v>
+        <v>18</v>
       </c>
       <c r="N309" s="2" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>30</v>
       </c>
       <c r="M312" s="12" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="N312" s="2" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>14</v>
       </c>
       <c r="M313" s="12" t="n">
-        <v>0.07142857142857142</v>
+        <v>1</v>
       </c>
       <c r="N313" s="2" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>54</v>
       </c>
       <c r="M316" s="12" t="n">
-        <v>0.03703703703703703</v>
+        <v>2</v>
       </c>
       <c r="N316" s="2" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>65</v>
       </c>
       <c r="M317" s="12" t="n">
-        <v>0.1384615384615385</v>
+        <v>9</v>
       </c>
       <c r="N317" s="2" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>98</v>
       </c>
       <c r="M318" s="12" t="n">
-        <v>0.01020408163265306</v>
+        <v>1</v>
       </c>
       <c r="N318" s="2" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>57</v>
       </c>
       <c r="M320" s="12" t="n">
-        <v>0.05263157894736842</v>
+        <v>3</v>
       </c>
       <c r="N320" s="2" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>94</v>
       </c>
       <c r="M321" s="12" t="n">
-        <v>0.2978723404255319</v>
+        <v>28</v>
       </c>
       <c r="N321" s="2" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>38</v>
       </c>
       <c r="M322" s="12" t="n">
-        <v>0.1578947368421053</v>
+        <v>6</v>
       </c>
       <c r="N322" s="2" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>98</v>
       </c>
       <c r="M324" s="12" t="n">
-        <v>0.07142857142857142</v>
+        <v>7</v>
       </c>
       <c r="N324" s="2" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>59</v>
       </c>
       <c r="M325" s="12" t="n">
-        <v>0.1525423728813559</v>
+        <v>9</v>
       </c>
       <c r="N325" s="2" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>78</v>
       </c>
       <c r="M326" s="12" t="n">
-        <v>0.2307692307692308</v>
+        <v>18</v>
       </c>
       <c r="N326" s="2" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>48</v>
       </c>
       <c r="M328" s="12" t="n">
-        <v>0.7708333333333334</v>
+        <v>37</v>
       </c>
       <c r="N328" s="2" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>101</v>
       </c>
       <c r="M330" s="12" t="n">
-        <v>0.0297029702970297</v>
+        <v>3</v>
       </c>
       <c r="N330" s="2" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>64</v>
       </c>
       <c r="M331" s="12" t="n">
-        <v>0.265625</v>
+        <v>17</v>
       </c>
       <c r="N331" s="2" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>66</v>
       </c>
       <c r="M332" s="12" t="n">
-        <v>0.01515151515151515</v>
+        <v>1</v>
       </c>
       <c r="N332" s="2" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>112</v>
       </c>
       <c r="M335" s="12" t="n">
-        <v>0.08035714285714286</v>
+        <v>9</v>
       </c>
       <c r="N335" s="2" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>55</v>
       </c>
       <c r="M337" s="12" t="n">
-        <v>0.01818181818181818</v>
+        <v>1</v>
       </c>
       <c r="N337" s="2" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>126</v>
       </c>
       <c r="M341" s="12" t="n">
-        <v>0.07142857142857142</v>
+        <v>9</v>
       </c>
       <c r="N341" s="2" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>40</v>
       </c>
       <c r="M343" s="12" t="n">
-        <v>0.075</v>
+        <v>3</v>
       </c>
       <c r="N343" s="2" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>64</v>
       </c>
       <c r="M344" s="12" t="n">
-        <v>0.0625</v>
+        <v>4</v>
       </c>
       <c r="N344" s="2" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>55</v>
       </c>
       <c r="M345" s="12" t="n">
-        <v>0.01818181818181818</v>
+        <v>1</v>
       </c>
       <c r="N345" s="2" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>39</v>
       </c>
       <c r="M346" s="12" t="n">
-        <v>0.1538461538461539</v>
+        <v>6</v>
       </c>
       <c r="N346" s="2" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>65</v>
       </c>
       <c r="M347" s="12" t="n">
-        <v>0.04615384615384616</v>
+        <v>3</v>
       </c>
       <c r="N347" s="2" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>45</v>
       </c>
       <c r="M348" s="12" t="n">
-        <v>0.02222222222222222</v>
+        <v>1</v>
       </c>
       <c r="N348" s="2" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>67</v>
       </c>
       <c r="M349" s="12" t="n">
-        <v>0.01492537313432836</v>
+        <v>1</v>
       </c>
       <c r="N349" s="2" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>54</v>
       </c>
       <c r="M350" s="12" t="n">
-        <v>0.09259259259259259</v>
+        <v>5</v>
       </c>
       <c r="N350" s="2" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>42</v>
       </c>
       <c r="M351" s="12" t="n">
-        <v>0.04761904761904762</v>
+        <v>2</v>
       </c>
       <c r="N351" s="2" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>31</v>
       </c>
       <c r="M352" s="12" t="n">
-        <v>0.03225806451612903</v>
+        <v>1</v>
       </c>
       <c r="N352" s="2" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>64</v>
       </c>
       <c r="M353" s="12" t="n">
-        <v>0.28125</v>
+        <v>18</v>
       </c>
       <c r="N353" s="2" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>22</v>
       </c>
       <c r="M354" s="12" t="n">
-        <v>0.04545454545454546</v>
+        <v>1</v>
       </c>
       <c r="N354" s="2" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>48</v>
       </c>
       <c r="M355" s="12" t="n">
-        <v>0.6041666666666666</v>
+        <v>29</v>
       </c>
       <c r="N355" s="2" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>110</v>
       </c>
       <c r="M356" s="12" t="n">
-        <v>0.1</v>
+        <v>11</v>
       </c>
       <c r="N356" s="2" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>55</v>
       </c>
       <c r="M357" s="12" t="n">
-        <v>0.2363636363636364</v>
+        <v>13</v>
       </c>
       <c r="N357" s="2" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>41</v>
       </c>
       <c r="M358" s="12" t="n">
-        <v>0.0975609756097561</v>
+        <v>4</v>
       </c>
       <c r="N358" s="2" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>48</v>
       </c>
       <c r="M359" s="12" t="n">
-        <v>0.375</v>
+        <v>18</v>
       </c>
       <c r="N359" s="2" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>134</v>
       </c>
       <c r="M361" s="12" t="n">
-        <v>0.01492537313432836</v>
+        <v>2</v>
       </c>
       <c r="N361" s="2" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>16</v>
       </c>
       <c r="M363" s="12" t="n">
-        <v>0.25</v>
+        <v>4</v>
       </c>
       <c r="N363" s="2" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         <v>74</v>
       </c>
       <c r="M364" s="12" t="n">
-        <v>0.02702702702702703</v>
+        <v>2</v>
       </c>
       <c r="N364" s="2" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>98</v>
       </c>
       <c r="M366" s="12" t="n">
-        <v>0.06122448979591837</v>
+        <v>6</v>
       </c>
       <c r="N366" s="2" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>55</v>
       </c>
       <c r="M367" s="12" t="n">
-        <v>0.07272727272727272</v>
+        <v>4</v>
       </c>
       <c r="N367" s="2" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>37</v>
       </c>
       <c r="M368" s="12" t="n">
-        <v>0.02702702702702703</v>
+        <v>1</v>
       </c>
       <c r="N368" s="2" t="inlineStr">
         <is>
@@ -20137,7 +20137,7 @@
         <v>75</v>
       </c>
       <c r="M369" s="12" t="n">
-        <v>0.01333333333333333</v>
+        <v>1</v>
       </c>
       <c r="N369" s="2" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>50</v>
       </c>
       <c r="M370" s="12" t="n">
-        <v>0.06</v>
+        <v>3</v>
       </c>
       <c r="N370" s="2" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>92</v>
       </c>
       <c r="M371" s="12" t="n">
-        <v>0.02173913043478261</v>
+        <v>2</v>
       </c>
       <c r="N371" s="2" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>97</v>
       </c>
       <c r="M372" s="12" t="n">
-        <v>0.03092783505154639</v>
+        <v>3</v>
       </c>
       <c r="N372" s="2" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>24</v>
       </c>
       <c r="M373" s="12" t="n">
-        <v>0.04166666666666666</v>
+        <v>1</v>
       </c>
       <c r="N373" s="2" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>36</v>
       </c>
       <c r="M375" s="12" t="n">
-        <v>0.1388888888888889</v>
+        <v>5</v>
       </c>
       <c r="N375" s="2" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>75</v>
       </c>
       <c r="M376" s="12" t="n">
-        <v>0.02666666666666667</v>
+        <v>2</v>
       </c>
       <c r="N376" s="2" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>28</v>
       </c>
       <c r="M377" s="12" t="n">
-        <v>0.2142857142857143</v>
+        <v>6</v>
       </c>
       <c r="N377" s="2" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>19</v>
       </c>
       <c r="M378" s="12" t="n">
-        <v>0.631578947368421</v>
+        <v>12</v>
       </c>
       <c r="N378" s="2" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>49</v>
       </c>
       <c r="M380" s="12" t="n">
-        <v>0.5510204081632653</v>
+        <v>27</v>
       </c>
       <c r="N380" s="2" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>34</v>
       </c>
       <c r="M383" s="12" t="n">
-        <v>0.02941176470588235</v>
+        <v>1</v>
       </c>
       <c r="N383" s="2" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>98</v>
       </c>
       <c r="M384" s="12" t="n">
-        <v>0.03061224489795918</v>
+        <v>3</v>
       </c>
       <c r="N384" s="2" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>72</v>
       </c>
       <c r="M385" s="12" t="n">
-        <v>0.09722222222222222</v>
+        <v>7</v>
       </c>
       <c r="N385" s="2" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>69</v>
       </c>
       <c r="M386" s="12" t="n">
-        <v>0.04347826086956522</v>
+        <v>3</v>
       </c>
       <c r="N386" s="2" t="inlineStr">
         <is>
@@ -21159,7 +21159,7 @@
         <v>57</v>
       </c>
       <c r="M388" s="12" t="n">
-        <v>0.01754385964912281</v>
+        <v>1</v>
       </c>
       <c r="N388" s="2" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>80</v>
       </c>
       <c r="M389" s="12" t="n">
-        <v>0.0125</v>
+        <v>1</v>
       </c>
       <c r="N389" s="2" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>31</v>
       </c>
       <c r="M390" s="12" t="n">
-        <v>0.3225806451612903</v>
+        <v>10</v>
       </c>
       <c r="N390" s="2" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>31</v>
       </c>
       <c r="M391" s="12" t="n">
-        <v>0.06451612903225806</v>
+        <v>2</v>
       </c>
       <c r="N391" s="2" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>68</v>
       </c>
       <c r="M394" s="12" t="n">
-        <v>0.02941176470588235</v>
+        <v>2</v>
       </c>
       <c r="N394" s="2" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>16</v>
       </c>
       <c r="M399" s="12" t="n">
-        <v>0.5625</v>
+        <v>9</v>
       </c>
       <c r="N399" s="2" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>47</v>
       </c>
       <c r="M404" s="12" t="n">
-        <v>0.0851063829787234</v>
+        <v>4</v>
       </c>
       <c r="N404" s="2" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>15</v>
       </c>
       <c r="M405" s="12" t="n">
-        <v>0.6666666666666666</v>
+        <v>10</v>
       </c>
       <c r="N405" s="2" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>46</v>
       </c>
       <c r="M406" s="12" t="n">
-        <v>0.4782608695652174</v>
+        <v>22</v>
       </c>
       <c r="N406" s="2" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45</v>
       </c>
       <c r="M411" s="12" t="n">
-        <v>0.06666666666666667</v>
+        <v>3</v>
       </c>
       <c r="N411" s="2" t="inlineStr">
         <is>
@@ -22509,7 +22509,7 @@
         <v>49</v>
       </c>
       <c r="M413" s="12" t="n">
-        <v>0.06122448979591837</v>
+        <v>3</v>
       </c>
       <c r="N413" s="2" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>24</v>
       </c>
       <c r="M414" s="12" t="n">
-        <v>0.2083333333333333</v>
+        <v>5</v>
       </c>
       <c r="N414" s="2" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>28</v>
       </c>
       <c r="M415" s="12" t="n">
-        <v>0.8571428571428571</v>
+        <v>24</v>
       </c>
       <c r="N415" s="2" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>22</v>
       </c>
       <c r="M416" s="12" t="n">
-        <v>0.09090909090909091</v>
+        <v>2</v>
       </c>
       <c r="N416" s="2" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>15</v>
       </c>
       <c r="M417" s="12" t="n">
-        <v>0.6666666666666666</v>
+        <v>10</v>
       </c>
       <c r="N417" s="2" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         <v>86</v>
       </c>
       <c r="M418" s="12" t="n">
-        <v>0.01162790697674419</v>
+        <v>1</v>
       </c>
       <c r="N418" s="2" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         <v>48</v>
       </c>
       <c r="M419" s="12" t="n">
-        <v>0.04166666666666666</v>
+        <v>2</v>
       </c>
       <c r="N419" s="2" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>23</v>
       </c>
       <c r="M420" s="12" t="n">
-        <v>0.6956521739130435</v>
+        <v>16</v>
       </c>
       <c r="N420" s="2" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         <v>43</v>
       </c>
       <c r="M421" s="12" t="n">
-        <v>0.06976744186046512</v>
+        <v>3</v>
       </c>
       <c r="N421" s="2" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>45</v>
       </c>
       <c r="M422" s="12" t="n">
-        <v>0.2444444444444444</v>
+        <v>11</v>
       </c>
       <c r="N422" s="2" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>36</v>
       </c>
       <c r="M423" s="12" t="n">
-        <v>0.05555555555555555</v>
+        <v>2</v>
       </c>
       <c r="N423" s="2" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>18</v>
       </c>
       <c r="M424" s="12" t="n">
-        <v>0.6666666666666666</v>
+        <v>12</v>
       </c>
       <c r="N424" s="2" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>55</v>
       </c>
       <c r="M425" s="12" t="n">
-        <v>0.1454545454545454</v>
+        <v>8</v>
       </c>
       <c r="N425" s="2" t="inlineStr">
         <is>
@@ -23207,7 +23207,7 @@
         <v>13</v>
       </c>
       <c r="M426" s="12" t="n">
-        <v>0.5384615384615384</v>
+        <v>7</v>
       </c>
       <c r="N426" s="2" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>60</v>
       </c>
       <c r="M427" s="12" t="n">
-        <v>0.2666666666666667</v>
+        <v>16</v>
       </c>
       <c r="N427" s="2" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>33</v>
       </c>
       <c r="M429" s="12" t="n">
-        <v>0.5757575757575758</v>
+        <v>19</v>
       </c>
       <c r="N429" s="2" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>26</v>
       </c>
       <c r="M430" s="12" t="n">
-        <v>0.03846153846153846</v>
+        <v>1</v>
       </c>
       <c r="N430" s="2" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>32</v>
       </c>
       <c r="M431" s="12" t="n">
-        <v>0.25</v>
+        <v>8</v>
       </c>
       <c r="N431" s="2" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>42</v>
       </c>
       <c r="M432" s="12" t="n">
-        <v>0.09523809523809523</v>
+        <v>4</v>
       </c>
       <c r="N432" s="2" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>46</v>
       </c>
       <c r="M434" s="12" t="n">
-        <v>0.1739130434782609</v>
+        <v>8</v>
       </c>
       <c r="N434" s="2" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>9</v>
       </c>
       <c r="M436" s="12" t="n">
-        <v>0.1111111111111111</v>
+        <v>1</v>
       </c>
       <c r="N436" s="2" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>35</v>
       </c>
       <c r="M438" s="12" t="n">
-        <v>0.02857142857142857</v>
+        <v>1</v>
       </c>
       <c r="N438" s="2" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>25</v>
       </c>
       <c r="M441" s="12" t="n">
-        <v>0.08</v>
+        <v>2</v>
       </c>
       <c r="N441" s="2" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>8</v>
       </c>
       <c r="M444" s="12" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="N444" s="2" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>58</v>
       </c>
       <c r="M449" s="12" t="n">
-        <v>0.05172413793103448</v>
+        <v>3</v>
       </c>
       <c r="N449" s="2" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>37</v>
       </c>
       <c r="M451" s="12" t="n">
-        <v>0.5945945945945946</v>
+        <v>22</v>
       </c>
       <c r="N451" s="2" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>60</v>
       </c>
       <c r="M454" s="12" t="n">
-        <v>0.01666666666666667</v>
+        <v>1</v>
       </c>
       <c r="N454" s="2" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>34</v>
       </c>
       <c r="M457" s="12" t="n">
-        <v>0.05882352941176471</v>
+        <v>2</v>
       </c>
       <c r="N457" s="2" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>95</v>
       </c>
       <c r="M458" s="12" t="n">
-        <v>0.01052631578947368</v>
+        <v>1</v>
       </c>
       <c r="N458" s="2" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>8</v>
       </c>
       <c r="M461" s="12" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="N461" s="2" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>42</v>
       </c>
       <c r="M467" s="12" t="n">
-        <v>0.02380952380952381</v>
+        <v>1</v>
       </c>
       <c r="N467" s="2" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>16</v>
       </c>
       <c r="M472" s="12" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="N472" s="2" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>25</v>
       </c>
       <c r="M474" s="12" t="n">
-        <v>0.08</v>
+        <v>2</v>
       </c>
       <c r="N474" s="2" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>10</v>
       </c>
       <c r="M476" s="12" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="N476" s="2" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>19</v>
       </c>
       <c r="M479" s="12" t="n">
-        <v>0.1052631578947368</v>
+        <v>2</v>
       </c>
       <c r="N479" s="2" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>33</v>
       </c>
       <c r="M482" s="12" t="n">
-        <v>0.09090909090909091</v>
+        <v>3</v>
       </c>
       <c r="N482" s="2" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>9</v>
       </c>
       <c r="M483" s="12" t="n">
-        <v>0.1111111111111111</v>
+        <v>1</v>
       </c>
       <c r="N483" s="2" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>16</v>
       </c>
       <c r="M484" s="12" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="N484" s="2" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>23</v>
       </c>
       <c r="M485" s="12" t="n">
-        <v>0.391304347826087</v>
+        <v>9</v>
       </c>
       <c r="N485" s="2" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>7</v>
       </c>
       <c r="M487" s="12" t="n">
-        <v>0.2857142857142857</v>
+        <v>2</v>
       </c>
       <c r="N487" s="2" t="inlineStr">
         <is>
@@ -26715,7 +26715,7 @@
         <v>27</v>
       </c>
       <c r="M492" s="12" t="n">
-        <v>0.03703703703703703</v>
+        <v>1</v>
       </c>
       <c r="N492" s="2" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>55</v>
       </c>
       <c r="M494" s="12" t="n">
-        <v>0.03636363636363636</v>
+        <v>2</v>
       </c>
       <c r="N494" s="2" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>17</v>
       </c>
       <c r="M496" s="12" t="n">
-        <v>0.05882352941176471</v>
+        <v>1</v>
       </c>
       <c r="N496" s="2" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>3</v>
       </c>
       <c r="M499" s="12" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="N499" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
+++ b/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
@@ -2916,7 +2916,11 @@
           <t>MERCOGLIANO</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
           <t>D'AMBROSIO RAFFAELLO</t>
@@ -3130,7 +3134,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3724,7 +3728,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4208,11 +4212,7 @@
           <t>PIACENZA</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C74" s="2" t="inlineStr"/>
       <c r="D74" s="2" t="inlineStr">
         <is>
           <t>GIURICIN ANTONIO</t>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -6638,11 +6638,7 @@
           <t>BORGOMANERO</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C119" s="2" t="inlineStr"/>
       <c r="D119" s="2" t="inlineStr"/>
       <c r="E119" s="12" t="n">
         <v>130</v>
@@ -6958,7 +6954,11 @@
           <t>PALERMO</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr"/>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
           <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
@@ -8952,7 +8952,11 @@
           <t>TRIESTE</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr"/>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
           <t>ZAMPIERI ANTONIO</t>
@@ -9544,7 +9548,7 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
@@ -12188,7 +12192,11 @@
           <t>VENEZIA</t>
         </is>
       </c>
-      <c r="C222" s="2" t="inlineStr"/>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
           <t>MARINI EMANUELE</t>
@@ -14722,7 +14730,11 @@
           <t>VITERBO</t>
         </is>
       </c>
-      <c r="C269" s="2" t="inlineStr"/>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
           <t>DELLA ROSA FABIO</t>
@@ -14772,7 +14784,11 @@
           <t>MONSUMMANO TERME</t>
         </is>
       </c>
-      <c r="C270" s="2" t="inlineStr"/>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
           <t>DE LUCA ANTONIO</t>
@@ -15038,7 +15054,11 @@
           <t>ROMA</t>
         </is>
       </c>
-      <c r="C275" s="2" t="inlineStr"/>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
           <t>CASINI GIUSEPPE NICCOLO'</t>
@@ -16870,7 +16890,11 @@
           <t>UDINE</t>
         </is>
       </c>
-      <c r="C309" s="2" t="inlineStr"/>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
           <t>FELICI FILIPPO</t>
@@ -18108,7 +18132,11 @@
           <t>TETTO GARETTO</t>
         </is>
       </c>
-      <c r="C332" s="2" t="inlineStr"/>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
           <t>SCIALO' MARCO</t>
@@ -19402,7 +19430,7 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
@@ -20318,7 +20346,11 @@
           <t>BORGO A MOZZANO</t>
         </is>
       </c>
-      <c r="C373" s="2" t="inlineStr"/>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
           <t>CASCIARI PAOLO</t>
@@ -20748,7 +20780,7 @@
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
@@ -21396,7 +21428,7 @@
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
@@ -21772,11 +21804,7 @@
           <t>SAN GIOVANNI LUPATOTO</t>
         </is>
       </c>
-      <c r="C400" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C400" s="2" t="inlineStr"/>
       <c r="D400" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -23122,7 +23150,11 @@
           <t>RAVENNA</t>
         </is>
       </c>
-      <c r="C425" s="2" t="inlineStr"/>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
           <t>CALIO' ANTONELLA</t>
@@ -23658,7 +23690,11 @@
           <t>MESSINA</t>
         </is>
       </c>
-      <c r="C435" s="2" t="inlineStr"/>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
           <t>MONTISANTI GIUSEPPE</t>
@@ -23708,7 +23744,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C436" s="2" t="inlineStr"/>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
           <t>ARMELLINI GIACOMO</t>
@@ -23814,7 +23854,7 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
@@ -23976,7 +24016,7 @@
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
@@ -24190,7 +24230,11 @@
           <t>SIENA</t>
         </is>
       </c>
-      <c r="C445" s="2" t="inlineStr"/>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
           <t>AMELIO ANTONIO FRANCESCO</t>
@@ -24294,7 +24338,11 @@
           <t>COLLESALVETTI</t>
         </is>
       </c>
-      <c r="C447" s="2" t="inlineStr"/>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
           <t>MUFFATO LORENZO</t>
@@ -24614,7 +24662,11 @@
           <t>COLLEGNO</t>
         </is>
       </c>
-      <c r="C453" s="2" t="inlineStr"/>
+      <c r="C453" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
           <t>GUERRA GIUSEPPE</t>
@@ -24934,7 +24986,11 @@
           <t>PENNE</t>
         </is>
       </c>
-      <c r="C459" s="2" t="inlineStr"/>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
           <t>CAIMMI ANDREA</t>
@@ -25686,7 +25742,11 @@
           <t>MORLUPO</t>
         </is>
       </c>
-      <c r="C473" s="2" t="inlineStr"/>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
           <t>DELLA ROSA FABIO</t>
@@ -25736,7 +25796,11 @@
           <t>BOMPORTO</t>
         </is>
       </c>
-      <c r="C474" s="2" t="inlineStr"/>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
           <t>LIBANORI FEDERICO</t>
@@ -25786,7 +25850,11 @@
           <t>ORICOLA</t>
         </is>
       </c>
-      <c r="C475" s="2" t="inlineStr"/>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
           <t>PACI CLAUDIO</t>
@@ -25944,11 +26012,7 @@
           <t>TORINO</t>
         </is>
       </c>
-      <c r="C478" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C478" s="2" t="inlineStr"/>
       <c r="D478" s="2" t="inlineStr">
         <is>
           <t>BRESCIA FEDERICO</t>
@@ -26160,11 +26224,7 @@
           <t>BREGNANO</t>
         </is>
       </c>
-      <c r="C482" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C482" s="2" t="inlineStr"/>
       <c r="D482" s="2" t="inlineStr"/>
       <c r="E482" s="12" t="n">
         <v>8</v>
@@ -26264,7 +26324,11 @@
           <t>ROMA</t>
         </is>
       </c>
-      <c r="C484" s="2" t="inlineStr"/>
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
           <t>MARIANI MARIO</t>
@@ -26368,11 +26432,7 @@
           <t>COLLEGNO</t>
         </is>
       </c>
-      <c r="C486" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C486" s="2" t="inlineStr"/>
       <c r="D486" s="2" t="inlineStr"/>
       <c r="E486" s="12" t="n">
         <v>7</v>
@@ -26580,7 +26640,11 @@
           <t>VITTORIO VENETO</t>
         </is>
       </c>
-      <c r="C490" s="2" t="inlineStr"/>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
           <t>MARCHIORI GIOVANNI AGOSTINO</t>
@@ -26630,11 +26694,7 @@
           <t>CANTÙ</t>
         </is>
       </c>
-      <c r="C491" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C491" s="2" t="inlineStr"/>
       <c r="D491" s="2" t="inlineStr">
         <is>
           <t>RAVA CLAUDIO</t>
@@ -26738,7 +26798,11 @@
           <t>SAN SALVO</t>
         </is>
       </c>
-      <c r="C493" s="2" t="inlineStr"/>
+      <c r="C493" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
           <t>D'ANNIBALE EMANUELE</t>
@@ -26788,7 +26852,11 @@
           <t>ROMA</t>
         </is>
       </c>
-      <c r="C494" s="2" t="inlineStr"/>
+      <c r="C494" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
           <t>LESTI LEONARDO</t>
@@ -26838,7 +26906,11 @@
           <t>BERCETO</t>
         </is>
       </c>
-      <c r="C495" s="2" t="inlineStr"/>
+      <c r="C495" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
           <t>IACOPINI ALESSANDRA</t>
@@ -26888,7 +26960,11 @@
           <t>MONTIGNOSO</t>
         </is>
       </c>
-      <c r="C496" s="2" t="inlineStr"/>
+      <c r="C496" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
           <t>CASCIARI PAOLO</t>
@@ -27690,11 +27766,7 @@
           <t>NOVARA</t>
         </is>
       </c>
-      <c r="C511" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C511" s="2" t="inlineStr"/>
       <c r="D511" s="2" t="inlineStr">
         <is>
           <t>BIANCHI ENRICO</t>
@@ -27798,7 +27870,11 @@
           <t>GASSINO TORINESE</t>
         </is>
       </c>
-      <c r="C513" s="2" t="inlineStr"/>
+      <c r="C513" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
           <t>BRESCIA FEDERICO</t>
@@ -28172,11 +28248,7 @@
           <t>PARMA</t>
         </is>
       </c>
-      <c r="C520" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
+      <c r="C520" s="2" t="inlineStr"/>
       <c r="D520" s="2" t="inlineStr">
         <is>
           <t>IACONA GIOVANNI</t>
@@ -28226,7 +28298,11 @@
           <t>FIDENZA</t>
         </is>
       </c>
-      <c r="C521" s="2" t="inlineStr"/>
+      <c r="C521" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
           <t>IACONA GIOVANNI</t>
@@ -28492,7 +28568,11 @@
           <t>MEDICINA</t>
         </is>
       </c>
-      <c r="C526" s="2" t="inlineStr"/>
+      <c r="C526" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
@@ -28542,7 +28622,11 @@
           <t>COPPARO</t>
         </is>
       </c>
-      <c r="C527" s="2" t="inlineStr"/>
+      <c r="C527" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D527" s="2" t="inlineStr">
         <is>
           <t>BASSI VALERIA</t>
@@ -28754,7 +28838,11 @@
           <t>SULMONA</t>
         </is>
       </c>
-      <c r="C531" s="2" t="inlineStr"/>
+      <c r="C531" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D531" s="2" t="inlineStr">
         <is>
           <t>COLOZZA STEFANO</t>
@@ -28804,7 +28892,11 @@
           <t>MONTECOSARO</t>
         </is>
       </c>
-      <c r="C532" s="2" t="inlineStr"/>
+      <c r="C532" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
           <t>STROLOGO FRANCESCO</t>
@@ -28854,7 +28946,11 @@
           <t>PESCARA</t>
         </is>
       </c>
-      <c r="C533" s="2" t="inlineStr"/>
+      <c r="C533" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D533" s="2" t="inlineStr">
         <is>
           <t>CAIMMI ANDREA</t>
@@ -28904,7 +29000,11 @@
           <t>MANOPPELLO</t>
         </is>
       </c>
-      <c r="C534" s="2" t="inlineStr"/>
+      <c r="C534" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
           <t>D'ANNIBALE EMANUELE</t>
@@ -29062,7 +29162,11 @@
           <t>LUCERA</t>
         </is>
       </c>
-      <c r="C537" s="2" t="inlineStr"/>
+      <c r="C537" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
           <t>CASCIANI GABRIELE</t>
@@ -29328,7 +29432,11 @@
           <t>PIANORO</t>
         </is>
       </c>
-      <c r="C542" s="2" t="inlineStr"/>
+      <c r="C542" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
       <c r="D542" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
@@ -29540,7 +29648,11 @@
           <t>BAGHERIA</t>
         </is>
       </c>
-      <c r="C546" s="2" t="inlineStr"/>
+      <c r="C546" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D546" s="2" t="inlineStr">
         <is>
           <t>CASSATA FULVIA</t>
@@ -29590,7 +29702,11 @@
           <t>FERENTINO</t>
         </is>
       </c>
-      <c r="C547" s="2" t="inlineStr"/>
+      <c r="C547" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D547" s="2" t="inlineStr">
         <is>
           <t>ERANDO FABIO</t>
@@ -29640,7 +29756,11 @@
           <t>ROMA</t>
         </is>
       </c>
-      <c r="C548" s="2" t="inlineStr"/>
+      <c r="C548" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D548" s="2" t="inlineStr">
         <is>
           <t>GIOVANNINI DANIELE</t>
@@ -29794,11 +29914,7 @@
           <t>IVREA</t>
         </is>
       </c>
-      <c r="C551" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C551" s="2" t="inlineStr"/>
       <c r="D551" s="2" t="inlineStr">
         <is>
           <t>DELLI CARRI LUCA</t>
@@ -29848,7 +29964,11 @@
           <t>CORRIDONIA</t>
         </is>
       </c>
-      <c r="C552" s="2" t="inlineStr"/>
+      <c r="C552" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D552" s="2" t="inlineStr">
         <is>
           <t>MORETTI MARCO MARIA</t>
@@ -29898,11 +30018,7 @@
           <t>PIACENZA</t>
         </is>
       </c>
-      <c r="C553" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C553" s="2" t="inlineStr"/>
       <c r="D553" s="2" t="inlineStr">
         <is>
           <t>GIURICIN ANTONIO</t>
@@ -29952,11 +30068,7 @@
           <t>MILANO</t>
         </is>
       </c>
-      <c r="C554" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C554" s="2" t="inlineStr"/>
       <c r="D554" s="2" t="inlineStr">
         <is>
           <t>RECCHIA ALESSANDRO</t>
@@ -30006,7 +30118,11 @@
           <t>SIENA</t>
         </is>
       </c>
-      <c r="C555" s="2" t="inlineStr"/>
+      <c r="C555" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D555" s="2" t="inlineStr">
         <is>
           <t>AMELIO ANTONIO FRANCESCO</t>
@@ -30056,7 +30172,11 @@
           <t>POMEZIA</t>
         </is>
       </c>
-      <c r="C556" s="2" t="inlineStr"/>
+      <c r="C556" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D556" s="2" t="inlineStr">
         <is>
           <t>ERANDO FABIO</t>
@@ -30106,7 +30226,11 @@
           <t>REGGIO DI CALABRIA</t>
         </is>
       </c>
-      <c r="C557" s="2" t="inlineStr"/>
+      <c r="C557" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D557" s="2" t="inlineStr">
         <is>
           <t>VERSACE RENATO</t>
@@ -30156,7 +30280,11 @@
           <t>AMELIA</t>
         </is>
       </c>
-      <c r="C558" s="2" t="inlineStr"/>
+      <c r="C558" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D558" s="2" t="inlineStr">
         <is>
           <t>CHIODI ROBERTO</t>

--- a/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
+++ b/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
@@ -27816,11 +27816,7 @@
           <t>ORBASSANO</t>
         </is>
       </c>
-      <c r="C512" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C512" s="2" t="inlineStr"/>
       <c r="D512" s="2" t="inlineStr">
         <is>
           <t>PODESTÀ ANDREA</t>
@@ -30388,11 +30384,7 @@
           <t>VALMADRERA</t>
         </is>
       </c>
-      <c r="C560" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C560" s="2" t="inlineStr"/>
       <c r="D560" s="2" t="inlineStr">
         <is>
           <t>ADINOLFI VINCENZO</t>

--- a/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
+++ b/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
@@ -810,11 +810,7 @@
           <t>PRATO</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
+      <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t>DE LUCA ANTONIO</t>
@@ -1028,7 +1024,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3188,7 +3184,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -4050,7 +4046,11 @@
           <t>PIACENZA</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
           <t>GIURICIN ANTONIO</t>
@@ -8042,7 +8042,11 @@
           <t>BORGOMANERO</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr"/>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="D145" s="2" t="inlineStr"/>
       <c r="E145" s="12" t="n">
         <v>130</v>
@@ -8144,7 +8148,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -12032,7 +12036,7 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -14786,7 +14790,7 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
@@ -16676,7 +16680,7 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Emanuele Marcelli</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
@@ -18134,7 +18138,7 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
@@ -18242,7 +18246,7 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
@@ -18458,7 +18462,7 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
@@ -19052,7 +19056,7 @@
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Emanuele Marcelli</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
@@ -19376,7 +19380,7 @@
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Emanuele Marcelli</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
@@ -21480,7 +21484,11 @@
           <t>SAN GIOVANNI LUPATOTO</t>
         </is>
       </c>
-      <c r="C394" s="2" t="inlineStr"/>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -23314,7 +23322,7 @@
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Emanuele Marcelli</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
@@ -23854,7 +23862,7 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
@@ -25204,7 +25212,7 @@
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Emanuele Marcelli</t>
         </is>
       </c>
       <c r="D463" s="2" t="inlineStr">
@@ -26174,7 +26182,11 @@
           <t>TORINO</t>
         </is>
       </c>
-      <c r="C481" s="2" t="inlineStr"/>
+      <c r="C481" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
           <t>BRESCIA FEDERICO</t>
@@ -26226,7 +26238,7 @@
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
@@ -26440,11 +26452,7 @@
           <t>LADISPOLI</t>
         </is>
       </c>
-      <c r="C486" s="2" t="inlineStr">
-        <is>
-          <t>Scagnetti Giampiero</t>
-        </is>
-      </c>
+      <c r="C486" s="2" t="inlineStr"/>
       <c r="D486" s="2" t="inlineStr">
         <is>
           <t>GIOVANNINI DANIELE</t>
@@ -26602,7 +26610,11 @@
           <t>BREGNANO</t>
         </is>
       </c>
-      <c r="C489" s="2" t="inlineStr"/>
+      <c r="C489" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="D489" s="2" t="inlineStr"/>
       <c r="E489" s="12" t="n">
         <v>8</v>
@@ -26810,7 +26822,11 @@
           <t>TELGATE</t>
         </is>
       </c>
-      <c r="C493" s="2" t="inlineStr"/>
+      <c r="C493" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
           <t>SALVINELLI LUCA</t>
@@ -26914,7 +26930,11 @@
           <t>COLLEGNO</t>
         </is>
       </c>
-      <c r="C495" s="2" t="inlineStr"/>
+      <c r="C495" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="D495" s="2" t="inlineStr"/>
       <c r="E495" s="12" t="n">
         <v>7</v>
@@ -27122,7 +27142,11 @@
           <t>CANTÙ</t>
         </is>
       </c>
-      <c r="C499" s="2" t="inlineStr"/>
+      <c r="C499" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
           <t>RAVA CLAUDIO</t>
@@ -28780,11 +28804,7 @@
           <t>COPPARO</t>
         </is>
       </c>
-      <c r="C530" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C530" s="2" t="inlineStr"/>
       <c r="D530" s="2" t="inlineStr">
         <is>
           <t>BASSI VALERIA</t>
@@ -28834,11 +28854,7 @@
           <t>PESARO</t>
         </is>
       </c>
-      <c r="C531" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C531" s="2" t="inlineStr"/>
       <c r="D531" s="2" t="inlineStr">
         <is>
           <t>DI VIRGILIO DAVID</t>
@@ -28996,11 +29012,7 @@
           <t>SULMONA</t>
         </is>
       </c>
-      <c r="C534" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C534" s="2" t="inlineStr"/>
       <c r="D534" s="2" t="inlineStr">
         <is>
           <t>COLOZZA STEFANO</t>
@@ -29050,11 +29062,7 @@
           <t>MONTECOSARO</t>
         </is>
       </c>
-      <c r="C535" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C535" s="2" t="inlineStr"/>
       <c r="D535" s="2" t="inlineStr">
         <is>
           <t>STROLOGO FRANCESCO</t>
@@ -29104,11 +29112,7 @@
           <t>PESCARA</t>
         </is>
       </c>
-      <c r="C536" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C536" s="2" t="inlineStr"/>
       <c r="D536" s="2" t="inlineStr">
         <is>
           <t>CAIMMI ANDREA</t>
@@ -29158,11 +29162,7 @@
           <t>MANOPPELLO</t>
         </is>
       </c>
-      <c r="C537" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C537" s="2" t="inlineStr"/>
       <c r="D537" s="2" t="inlineStr">
         <is>
           <t>D'ANNIBALE EMANUELE</t>
@@ -29320,11 +29320,7 @@
           <t>LUCERA</t>
         </is>
       </c>
-      <c r="C540" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C540" s="2" t="inlineStr"/>
       <c r="D540" s="2" t="inlineStr">
         <is>
           <t>CASCIANI GABRIELE</t>
@@ -29806,11 +29802,7 @@
           <t>BAGHERIA</t>
         </is>
       </c>
-      <c r="C549" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C549" s="2" t="inlineStr"/>
       <c r="D549" s="2" t="inlineStr">
         <is>
           <t>CASSATA FULVIA</t>
@@ -29860,11 +29852,7 @@
           <t>FERENTINO</t>
         </is>
       </c>
-      <c r="C550" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C550" s="2" t="inlineStr"/>
       <c r="D550" s="2" t="inlineStr">
         <is>
           <t>ERANDO FABIO</t>
@@ -29914,11 +29902,7 @@
           <t>ROMA</t>
         </is>
       </c>
-      <c r="C551" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C551" s="2" t="inlineStr"/>
       <c r="D551" s="2" t="inlineStr">
         <is>
           <t>GIOVANNINI DANIELE</t>
@@ -29968,11 +29952,7 @@
           <t>ROMA</t>
         </is>
       </c>
-      <c r="C552" s="2" t="inlineStr">
-        <is>
-          <t>Scagnetti Giampiero</t>
-        </is>
-      </c>
+      <c r="C552" s="2" t="inlineStr"/>
       <c r="D552" s="2" t="inlineStr">
         <is>
           <t>CASINI GIUSEPPE NICCOLO'</t>
@@ -30022,11 +30002,7 @@
           <t>CAPENA</t>
         </is>
       </c>
-      <c r="C553" s="2" t="inlineStr">
-        <is>
-          <t>Scagnetti Giampiero</t>
-        </is>
-      </c>
+      <c r="C553" s="2" t="inlineStr"/>
       <c r="D553" s="2" t="inlineStr"/>
       <c r="E553" s="12" t="n">
         <v>0</v>
@@ -30122,11 +30098,7 @@
           <t>CORRIDONIA</t>
         </is>
       </c>
-      <c r="C555" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C555" s="2" t="inlineStr"/>
       <c r="D555" s="2" t="inlineStr">
         <is>
           <t>MORETTI MARCO MARIA</t>
@@ -30276,11 +30248,7 @@
           <t>SIENA</t>
         </is>
       </c>
-      <c r="C558" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C558" s="2" t="inlineStr"/>
       <c r="D558" s="2" t="inlineStr">
         <is>
           <t>AMELIO ANTONIO FRANCESCO</t>
@@ -30330,11 +30298,7 @@
           <t>POMEZIA</t>
         </is>
       </c>
-      <c r="C559" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C559" s="2" t="inlineStr"/>
       <c r="D559" s="2" t="inlineStr">
         <is>
           <t>ERANDO FABIO</t>
@@ -30384,11 +30348,7 @@
           <t>REGGIO DI CALABRIA</t>
         </is>
       </c>
-      <c r="C560" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C560" s="2" t="inlineStr"/>
       <c r="D560" s="2" t="inlineStr">
         <is>
           <t>VERSACE RENATO</t>
@@ -30438,11 +30398,7 @@
           <t>AMELIA</t>
         </is>
       </c>
-      <c r="C561" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C561" s="2" t="inlineStr"/>
       <c r="D561" s="2" t="inlineStr">
         <is>
           <t>CHIODI ROBERTO</t>

--- a/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
+++ b/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
@@ -2968,7 +2968,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -14628,7 +14628,7 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
@@ -15222,7 +15222,7 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
@@ -19434,7 +19434,7 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
@@ -22890,7 +22890,7 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
@@ -24834,7 +24834,7 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
@@ -26182,11 +26182,7 @@
           <t>TORINO</t>
         </is>
       </c>
-      <c r="C481" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C481" s="2" t="inlineStr"/>
       <c r="D481" s="2" t="inlineStr">
         <is>
           <t>BRESCIA FEDERICO</t>
@@ -26930,11 +26926,7 @@
           <t>COLLEGNO</t>
         </is>
       </c>
-      <c r="C495" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C495" s="2" t="inlineStr"/>
       <c r="D495" s="2" t="inlineStr"/>
       <c r="E495" s="12" t="n">
         <v>7</v>
@@ -27142,11 +27134,7 @@
           <t>CANTÙ</t>
         </is>
       </c>
-      <c r="C499" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C499" s="2" t="inlineStr"/>
       <c r="D499" s="2" t="inlineStr">
         <is>
           <t>RAVA CLAUDIO</t>
@@ -28216,7 +28204,7 @@
       </c>
       <c r="C519" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D519" s="2" t="inlineStr">
@@ -29370,11 +29358,7 @@
           <t>ALBA</t>
         </is>
       </c>
-      <c r="C541" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
+      <c r="C541" s="2" t="inlineStr"/>
       <c r="D541" s="2" t="inlineStr">
         <is>
           <t>GIARRATANA SEARA</t>

--- a/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
+++ b/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
@@ -26606,11 +26606,7 @@
           <t>BREGNANO</t>
         </is>
       </c>
-      <c r="C489" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C489" s="2" t="inlineStr"/>
       <c r="D489" s="2" t="inlineStr"/>
       <c r="E489" s="12" t="n">
         <v>8</v>

--- a/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
+++ b/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3884,11 +3884,7 @@
           <t>RAVENNA</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C68" s="2" t="inlineStr"/>
       <c r="D68" s="2" t="inlineStr">
         <is>
           <t>CALIO' ANTONELLA</t>
@@ -5452,7 +5448,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -15382,11 +15378,7 @@
           <t>RAVENNA</t>
         </is>
       </c>
-      <c r="C281" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C281" s="2" t="inlineStr"/>
       <c r="D281" s="2" t="inlineStr">
         <is>
           <t>CALIO' ANTONELLA</t>
@@ -16248,7 +16240,7 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
@@ -20406,7 +20398,7 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
@@ -21486,7 +21478,7 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
@@ -21538,11 +21530,7 @@
           <t>COTIGNOLA</t>
         </is>
       </c>
-      <c r="C395" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C395" s="2" t="inlineStr"/>
       <c r="D395" s="2" t="inlineStr">
         <is>
           <t>CALIO' ANTONELLA</t>
@@ -25750,11 +25738,7 @@
           <t>RAVENNA</t>
         </is>
       </c>
-      <c r="C473" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C473" s="2" t="inlineStr"/>
       <c r="D473" s="2" t="inlineStr">
         <is>
           <t>CALIO' ANTONELLA</t>
@@ -28036,11 +28020,7 @@
           <t>GASSINO TORINESE</t>
         </is>
       </c>
-      <c r="C516" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
+      <c r="C516" s="2" t="inlineStr"/>
       <c r="D516" s="2" t="inlineStr">
         <is>
           <t>BRESCIA FEDERICO</t>
@@ -28144,11 +28124,7 @@
           <t>ALASSIO</t>
         </is>
       </c>
-      <c r="C518" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
+      <c r="C518" s="2" t="inlineStr"/>
       <c r="D518" s="2" t="inlineStr">
         <is>
           <t>BARNABA SALVATORE</t>
@@ -28252,11 +28228,7 @@
           <t>CASAZZA</t>
         </is>
       </c>
-      <c r="C520" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
+      <c r="C520" s="2" t="inlineStr"/>
       <c r="D520" s="2" t="inlineStr">
         <is>
           <t>BRIGNOLI STEFANO</t>
@@ -28306,11 +28278,7 @@
           <t>PIANICO</t>
         </is>
       </c>
-      <c r="C521" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
+      <c r="C521" s="2" t="inlineStr"/>
       <c r="D521" s="2" t="inlineStr">
         <is>
           <t>BRIGNOLI STEFANO</t>
@@ -28360,11 +28328,7 @@
           <t>BAGNOLO SAN VITO</t>
         </is>
       </c>
-      <c r="C522" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
+      <c r="C522" s="2" t="inlineStr"/>
       <c r="D522" s="2" t="inlineStr">
         <is>
           <t>CARMINATI SIMONE</t>
@@ -28464,11 +28428,7 @@
           <t>FIDENZA</t>
         </is>
       </c>
-      <c r="C524" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
+      <c r="C524" s="2" t="inlineStr"/>
       <c r="D524" s="2" t="inlineStr">
         <is>
           <t>IACONA GIOVANNI</t>
@@ -28518,11 +28478,7 @@
           <t>ALA</t>
         </is>
       </c>
-      <c r="C525" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C525" s="2" t="inlineStr"/>
       <c r="D525" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -28572,11 +28528,7 @@
           <t>TRENTO</t>
         </is>
       </c>
-      <c r="C526" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C526" s="2" t="inlineStr"/>
       <c r="D526" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -28626,11 +28578,7 @@
           <t>SONA</t>
         </is>
       </c>
-      <c r="C527" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C527" s="2" t="inlineStr"/>
       <c r="D527" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -28734,11 +28682,7 @@
           <t>MEDICINA</t>
         </is>
       </c>
-      <c r="C529" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
+      <c r="C529" s="2" t="inlineStr"/>
       <c r="D529" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
@@ -29458,11 +29402,7 @@
           <t>SPILIMBERGO</t>
         </is>
       </c>
-      <c r="C543" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C543" s="2" t="inlineStr"/>
       <c r="D543" s="2" t="inlineStr">
         <is>
           <t>ZANCANARO SANDRO</t>
@@ -29566,11 +29506,7 @@
           <t>PIANORO</t>
         </is>
       </c>
-      <c r="C545" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
+      <c r="C545" s="2" t="inlineStr"/>
       <c r="D545" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
@@ -30478,11 +30414,7 @@
           <t>VERONA</t>
         </is>
       </c>
-      <c r="C563" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C563" s="2" t="inlineStr"/>
       <c r="D563" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -30532,11 +30464,7 @@
           <t>TRIESTE</t>
         </is>
       </c>
-      <c r="C564" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C564" s="2" t="inlineStr"/>
       <c r="D564" s="2" t="inlineStr">
         <is>
           <t>ZAMPIERI ANTONIO</t>
@@ -30640,11 +30568,7 @@
           <t>VILLAFRANCA DI VERONA</t>
         </is>
       </c>
-      <c r="C566" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C566" s="2" t="inlineStr"/>
       <c r="D566" s="2" t="inlineStr">
         <is>
           <t>TBD</t>

--- a/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
+++ b/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N568" headerRowCount="1">
-  <autoFilter ref="A10:N568"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N574" headerRowCount="1">
+  <autoFilter ref="A10:N574"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N568"/>
+  <dimension ref="A1:N574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,7 +673,7 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>52163</v>
@@ -30703,6 +30703,326 @@
         </is>
       </c>
     </row>
+    <row r="569">
+      <c r="A569" s="2" t="inlineStr">
+        <is>
+          <t>02667</t>
+        </is>
+      </c>
+      <c r="B569" s="2" t="inlineStr">
+        <is>
+          <t>PIACENZA</t>
+        </is>
+      </c>
+      <c r="C569" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D569" s="2" t="inlineStr">
+        <is>
+          <t>GIURICIN ANTONIO</t>
+        </is>
+      </c>
+      <c r="E569" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F569" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G569" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H569" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I569" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J569" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K569" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L569" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M569" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N569" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="inlineStr">
+        <is>
+          <t>05920</t>
+        </is>
+      </c>
+      <c r="B570" s="2" t="inlineStr">
+        <is>
+          <t>FORLI'</t>
+        </is>
+      </c>
+      <c r="C570" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="D570" s="2" t="inlineStr"/>
+      <c r="E570" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F570" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G570" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H570" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I570" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J570" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K570" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L570" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M570" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N570" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="2" t="inlineStr">
+        <is>
+          <t>14289</t>
+        </is>
+      </c>
+      <c r="B571" s="2" t="inlineStr">
+        <is>
+          <t>SAN DANIELE DEL FRIULI</t>
+        </is>
+      </c>
+      <c r="C571" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="D571" s="2" t="inlineStr">
+        <is>
+          <t>FELICI FILIPPO</t>
+        </is>
+      </c>
+      <c r="E571" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F571" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G571" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H571" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I571" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J571" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K571" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L571" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M571" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N571" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="inlineStr">
+        <is>
+          <t>16435</t>
+        </is>
+      </c>
+      <c r="B572" s="2" t="inlineStr">
+        <is>
+          <t>CORREGGIO</t>
+        </is>
+      </c>
+      <c r="C572" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D572" s="2" t="inlineStr">
+        <is>
+          <t>IACOPINI ALESSANDRA</t>
+        </is>
+      </c>
+      <c r="E572" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F572" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G572" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H572" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I572" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J572" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K572" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L572" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M572" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N572" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="2" t="inlineStr">
+        <is>
+          <t>22973</t>
+        </is>
+      </c>
+      <c r="B573" s="2" t="inlineStr">
+        <is>
+          <t>FIDENZA</t>
+        </is>
+      </c>
+      <c r="C573" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D573" s="2" t="inlineStr">
+        <is>
+          <t>IACOPINI ALESSANDRA</t>
+        </is>
+      </c>
+      <c r="E573" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F573" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G573" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H573" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I573" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J573" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K573" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L573" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M573" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N573" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="inlineStr">
+        <is>
+          <t>23973</t>
+        </is>
+      </c>
+      <c r="B574" s="2" t="inlineStr">
+        <is>
+          <t>MUSSOLENTE</t>
+        </is>
+      </c>
+      <c r="C574" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="D574" s="2" t="inlineStr">
+        <is>
+          <t>CARRARO COSA MIHAI EMILIAN</t>
+        </is>
+      </c>
+      <c r="E574" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F574" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G574" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H574" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I574" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J574" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K574" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L574" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M574" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N574" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
+++ b/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
@@ -16672,7 +16672,7 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>Emanuele Marcelli</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
@@ -19048,7 +19048,7 @@
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>Emanuele Marcelli</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
@@ -19372,7 +19372,7 @@
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>Emanuele Marcelli</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
@@ -23310,7 +23310,7 @@
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>Emanuele Marcelli</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
@@ -25200,7 +25200,7 @@
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>Emanuele Marcelli</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D463" s="2" t="inlineStr">

--- a/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
+++ b/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
@@ -23703,11 +23703,7 @@
           <t>VIA CERCA  FRAZ.CALEPPIO 21</t>
         </is>
       </c>
-      <c r="D399" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="D399" s="2" t="inlineStr"/>
       <c r="E399" s="2" t="inlineStr">
         <is>
           <t>CERRI SARA</t>

--- a/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
+++ b/docs/files/REPORT_FILTRI/Tutti i punti vendita.xlsx
@@ -893,7 +893,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>LANZANTE DOMENICO</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>BRAVI MATTEO</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>MARCHIORI GIOVANNI AGOSTINO</t>
+          <t>GERBO ANDREA</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>GERBO ANDREA</t>
+          <t>MARINI EMANUELE</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>MARCHIORI GIOVANNI AGOSTINO</t>
+          <t>GERBO ANDREA</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F84" s="12" t="n">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>ZOTTI VINCENZO MARIA</t>
         </is>
       </c>
       <c r="F85" s="12" t="n">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F92" s="12" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F98" s="12" t="n">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>LANZANTE DOMENICO</t>
         </is>
       </c>
       <c r="F102" s="12" t="n">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>GERBO ANDREA</t>
+          <t>MARTELLATO MARCO</t>
         </is>
       </c>
       <c r="F103" s="12" t="n">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>LANZANTE DOMENICO</t>
         </is>
       </c>
       <c r="F129" s="12" t="n">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>ZOTTI VINCENZO MARIA</t>
         </is>
       </c>
       <c r="F172" s="12" t="n">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>LANZANTE DOMENICO</t>
         </is>
       </c>
       <c r="F180" s="12" t="n">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F186" s="12" t="n">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F192" s="12" t="n">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F194" s="12" t="n">
@@ -11684,7 +11684,11 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr"/>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>SVANINI EDOARDO</t>
+        </is>
+      </c>
       <c r="F195" s="12" t="n">
         <v>130</v>
       </c>
@@ -11741,7 +11745,7 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>BRAVI MATTEO</t>
         </is>
       </c>
       <c r="F196" s="12" t="n">
@@ -12095,7 +12099,7 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>LANZANTE DOMENICO</t>
         </is>
       </c>
       <c r="F202" s="12" t="n">
@@ -12567,7 +12571,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F210" s="12" t="n">
@@ -13629,7 +13633,7 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F228" s="12" t="n">
@@ -13865,7 +13869,7 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F232" s="12" t="n">
@@ -14042,7 +14046,7 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F235" s="12" t="n">
@@ -14514,7 +14518,7 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F243" s="12" t="n">
@@ -14809,7 +14813,7 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>MARCHIORI GIOVANNI AGOSTINO</t>
+          <t>GERBO ANDREA</t>
         </is>
       </c>
       <c r="F248" s="12" t="n">
@@ -15458,7 +15462,7 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F259" s="12" t="n">
@@ -16343,7 +16347,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F274" s="12" t="n">
@@ -16461,7 +16465,7 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F276" s="12" t="n">
@@ -16579,7 +16583,7 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F278" s="12" t="n">
@@ -17228,7 +17232,7 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>BRAVI MATTEO</t>
         </is>
       </c>
       <c r="F289" s="12" t="n">
@@ -17877,7 +17881,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F300" s="12" t="n">
@@ -18290,7 +18294,7 @@
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F307" s="12" t="n">
@@ -18349,7 +18353,7 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>BRAVI MATTEO</t>
         </is>
       </c>
       <c r="F308" s="12" t="n">
@@ -18821,7 +18825,7 @@
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>BRAVI MATTEO</t>
         </is>
       </c>
       <c r="F316" s="12" t="n">
@@ -19647,7 +19651,7 @@
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>MARCHIORI GIOVANNI AGOSTINO</t>
+          <t>GERBO ANDREA</t>
         </is>
       </c>
       <c r="F330" s="12" t="n">
@@ -19824,7 +19828,7 @@
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>GERBO ANDREA</t>
+          <t>MARINI EMANUELE</t>
         </is>
       </c>
       <c r="F333" s="12" t="n">
@@ -19883,7 +19887,7 @@
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F334" s="12" t="n">
@@ -19942,7 +19946,7 @@
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F335" s="12" t="n">
@@ -20178,7 +20182,7 @@
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DALLORTO ILARIA</t>
         </is>
       </c>
       <c r="F339" s="12" t="n">
@@ -20355,7 +20359,7 @@
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F342" s="12" t="n">
@@ -21177,7 +21181,7 @@
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F356" s="12" t="n">
@@ -21295,7 +21299,7 @@
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F358" s="12" t="n">
@@ -21649,7 +21653,7 @@
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F364" s="12" t="n">
@@ -22707,7 +22711,7 @@
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F382" s="12" t="n">
@@ -23179,7 +23183,7 @@
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>D'ANDREA PIERFRANCESCO</t>
         </is>
       </c>
       <c r="F390" s="12" t="n">
@@ -23474,7 +23478,7 @@
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F395" s="12" t="n">
@@ -24060,7 +24064,7 @@
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F405" s="12" t="n">
@@ -24119,7 +24123,7 @@
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>ZOTTI VINCENZO MARIA</t>
         </is>
       </c>
       <c r="F406" s="12" t="n">
@@ -24414,7 +24418,7 @@
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F411" s="12" t="n">
@@ -24707,11 +24711,7 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="E416" s="2" t="inlineStr">
-        <is>
-          <t>BRESCIA FEDERICO</t>
-        </is>
-      </c>
+      <c r="E416" s="2" t="inlineStr"/>
       <c r="F416" s="12" t="n">
         <v>42</v>
       </c>
@@ -25004,7 +25004,7 @@
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F421" s="12" t="n">
@@ -26701,11 +26701,7 @@
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr"/>
-      <c r="E450" s="2" t="inlineStr">
-        <is>
-          <t>CELLINI LUCA</t>
-        </is>
-      </c>
+      <c r="E450" s="2" t="inlineStr"/>
       <c r="F450" s="12" t="n">
         <v>29</v>
       </c>
@@ -27175,7 +27171,7 @@
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F458" s="12" t="n">
@@ -27352,7 +27348,7 @@
       </c>
       <c r="E461" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F461" s="12" t="n">
@@ -27879,7 +27875,7 @@
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>MARCHIORI GIOVANNI AGOSTINO</t>
+          <t>GERBO ANDREA</t>
         </is>
       </c>
       <c r="F470" s="12" t="n">
@@ -28174,7 +28170,7 @@
       </c>
       <c r="E475" s="2" t="inlineStr">
         <is>
-          <t>MARLETTA ELEONORA SOFIA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F475" s="12" t="n">
@@ -29810,7 +29806,7 @@
       </c>
       <c r="E503" s="2" t="inlineStr">
         <is>
-          <t>D'ANDREA PIERFRANCESCO</t>
+          <t>MARCHIORI GIOVANNI AGOSTINO</t>
         </is>
       </c>
       <c r="F503" s="12" t="n">
@@ -30042,7 +30038,7 @@
       </c>
       <c r="E507" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F507" s="12" t="n">
@@ -30154,7 +30150,11 @@
         </is>
       </c>
       <c r="D509" s="2" t="inlineStr"/>
-      <c r="E509" s="2" t="inlineStr"/>
+      <c r="E509" s="2" t="inlineStr">
+        <is>
+          <t>RAVA CLAUDIO</t>
+        </is>
+      </c>
       <c r="F509" s="12" t="n">
         <v>8</v>
       </c>
@@ -30323,7 +30323,11 @@
         </is>
       </c>
       <c r="D512" s="2" t="inlineStr"/>
-      <c r="E512" s="2" t="inlineStr"/>
+      <c r="E512" s="2" t="inlineStr">
+        <is>
+          <t>GUERRA GIUSEPPE</t>
+        </is>
+      </c>
       <c r="F512" s="12" t="n">
         <v>7</v>
       </c>
@@ -30726,7 +30730,7 @@
       </c>
       <c r="E519" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>ZOTTI VINCENZO MARIA</t>
         </is>
       </c>
       <c r="F519" s="12" t="n">
@@ -31017,7 +31021,7 @@
       </c>
       <c r="E524" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>MARTELLATO MARCO</t>
         </is>
       </c>
       <c r="F524" s="12" t="n">
@@ -31858,7 +31862,7 @@
       <c r="D539" s="2" t="inlineStr"/>
       <c r="E539" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>BRAVI MATTEO</t>
         </is>
       </c>
       <c r="F539" s="12" t="n">
@@ -31913,7 +31917,7 @@
       <c r="D540" s="2" t="inlineStr"/>
       <c r="E540" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="F540" s="12" t="n">
@@ -31968,7 +31972,7 @@
       <c r="D541" s="2" t="inlineStr"/>
       <c r="E541" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>MARCHIORI GIOVANNI AGOSTINO</t>
         </is>
       </c>
       <c r="F541" s="12" t="n">
@@ -32023,7 +32027,7 @@
       <c r="D542" s="2" t="inlineStr"/>
       <c r="E542" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>MARCHIORI GIOVANNI AGOSTINO</t>
         </is>
       </c>
       <c r="F542" s="12" t="n">
@@ -32078,7 +32082,7 @@
       <c r="D543" s="2" t="inlineStr"/>
       <c r="E543" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F543" s="12" t="n">
@@ -32247,7 +32251,7 @@
       <c r="D546" s="2" t="inlineStr"/>
       <c r="E546" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F546" s="12" t="n">
@@ -32927,7 +32931,7 @@
       </c>
       <c r="E558" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F558" s="12" t="n">
@@ -33214,7 +33218,7 @@
       </c>
       <c r="E563" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F563" s="12" t="n">
@@ -33654,7 +33658,7 @@
       <c r="D571" s="2" t="inlineStr"/>
       <c r="E571" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F571" s="12" t="n">
@@ -34094,7 +34098,7 @@
       <c r="D579" s="2" t="inlineStr"/>
       <c r="E579" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F579" s="12" t="n">
@@ -34208,7 +34212,7 @@
       </c>
       <c r="E581" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F581" s="12" t="n">
@@ -34263,7 +34267,7 @@
       <c r="D582" s="2" t="inlineStr"/>
       <c r="E582" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F582" s="12" t="n">
